--- a/03_process_editions/SV0001/input/SV0001_variables_survey.xlsx
+++ b/03_process_editions/SV0001/input/SV0001_variables_survey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\021_SVbevraging\01_code\03_process_editions\SV0001\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57EE1EBB-B7D3-4CC1-A0BE-C61A8FB88E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C003C8-E22A-4111-B3D0-D62D2D3C0DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="17172" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="surveydata" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
   <si>
     <t>variable</t>
   </si>
@@ -31,9 +31,6 @@
     <t>concept_id</t>
   </si>
   <si>
-    <t>variable_label</t>
-  </si>
-  <si>
     <t>Ingevuld</t>
   </si>
   <si>
@@ -335,156 +332,6 @@
   </si>
   <si>
     <t>QRcode</t>
-  </si>
-  <si>
-    <t>Werd de enquête schriftelijk geretourneerd of via internet?</t>
-  </si>
-  <si>
-    <t>Wat is uw geslacht?</t>
-  </si>
-  <si>
-    <t>In welk jaar en welke maand bent u geboren? JAAR</t>
-  </si>
-  <si>
-    <t>In welk jaar en welke maand bent u geboren? MAAND</t>
-  </si>
-  <si>
-    <t>In welke situatie bevindt u zich momenteel? </t>
-  </si>
-  <si>
-    <t>Anders (omschrijf) :</t>
-  </si>
-  <si>
-    <t>Wat is het hoogste diploma dat u heeft behaald? </t>
-  </si>
-  <si>
-    <t>Anders (omschrijf):</t>
-  </si>
-  <si>
-    <t>Hoe omschrijft u uw woonomgeving?</t>
-  </si>
-  <si>
-    <t>Ander (omschrijf) :</t>
-  </si>
-  <si>
-    <t>[Met een partner] Met welke mensen leeft u samen in uw woning?    Meerdere antwoorden mogelijk</t>
-  </si>
-  <si>
-    <t>[Met kinderen (ook in co-ouderschap, ook volwassen kinderen)] Met welke mensen leeft u samen in uw woning?    Meerdere antwoorden mogelijk</t>
-  </si>
-  <si>
-    <t>[Met ouder(s) ] Met welke mensen leeft u samen in uw woning?    Meerdere antwoorden mogelijk</t>
-  </si>
-  <si>
-    <t>[Met andere familieleden] Met welke mensen leeft u samen in uw woning?    Meerdere antwoorden mogelijk</t>
-  </si>
-  <si>
-    <t>[Met andere, niet familie (omschrijf) :] Met welke mensen leeft u samen in uw woning?    Meerdere antwoorden mogelijk</t>
-  </si>
-  <si>
-    <t>Met andere, niet familie (omschrijf) :</t>
-  </si>
-  <si>
-    <t>[Ik woon alleen ] Met welke mensen leeft u samen in uw woning?    Meerdere antwoorden mogelijk</t>
-  </si>
-  <si>
-    <t>[Weet niet/geen antwoord] Met welke mensen leeft u samen in uw woning?    Meerdere antwoorden mogelijk</t>
-  </si>
-  <si>
-    <t>In welke mate kan uw gezin rondkomen met het beschikbare inkomen?</t>
-  </si>
-  <si>
-    <t>Hoe vaak voelt u zich onveilig in uw buurt of wijk?</t>
-  </si>
-  <si>
-    <t>Hoe vaak mijdt u bepaalde plekken in uw gemeente of stad omdat u het er niet veilig vindt?</t>
-  </si>
-  <si>
-    <t>Hoe dikwijls ontmoet u niet-inwonende familie?</t>
-  </si>
-  <si>
-    <t>Hoe dikwijls ontmoet u vrienden of kennissen?</t>
-  </si>
-  <si>
-    <t>Hoe dikwijls ontmoet u buren?</t>
-  </si>
-  <si>
-    <t>Hoe vaak heeft u zelf de afgelopen 12 maanden zieke, gehandicapte of bejaarde familieleden, kennissen of buren geholpen of verzorgd?</t>
-  </si>
-  <si>
-    <t>‘De Vlaamse overheid is klantgericht’</t>
-  </si>
-  <si>
-    <t>’De Vlaamse overheid is transparant’</t>
-  </si>
-  <si>
-    <t>‘De Vlaamse overheid is efficiënt’</t>
-  </si>
-  <si>
-    <t>‘De Vlaamse overheid is vernieuwend’</t>
-  </si>
-  <si>
-    <t>‘De Vlaamse overheid is toegankelijk'</t>
-  </si>
-  <si>
-    <t>Hoe tevreden bent u in het algemeen over het beleid van uw lokale overheid?  U kan antwoorden met een score van 0 (heel ontevreden) tot 10 (heel tevreden).</t>
-  </si>
-  <si>
-    <t>Hoe tevreden bent u in het algemeen over het beleid van uw provinciale overheid?  U kan antwoorden met een score van 0 (heel ontevreden) tot 10 (heel tevreden).</t>
-  </si>
-  <si>
-    <t>Hoe tevreden bent u in het algemeen over het beleid van de Vlaamse overheid?   U kan antwoorden met een score van 0 (heel ontevreden) tot 10 (heel tevreden).</t>
-  </si>
-  <si>
-    <t>Hoe tevreden bent u in het algemeen over het beleid van de federale (Belgische) overheid?   U kan antwoorden met een score van 0 (heel ontevreden) tot 10 (heel tevreden).</t>
-  </si>
-  <si>
-    <t>Hoe tevreden bent u in het algemeen over het beleid van de Europese overheid?   U kan antwoorden met een score van 0 (heel ontevreden) tot 10 (heel tevreden).</t>
-  </si>
-  <si>
-    <t>‘De Vlaamse overheid geeft voldoende informatie’</t>
-  </si>
-  <si>
-    <t>‘De Vlaamse overheid geeft tijdig informatie’</t>
-  </si>
-  <si>
-    <t>‘De Vlaamse overheid geeft correcte informatie’</t>
-  </si>
-  <si>
-    <t>‘De Vlaamse overheid is duidelijk’</t>
-  </si>
-  <si>
-    <t>Hoeveel vertrouwen heeft u in uw lokale overheid?</t>
-  </si>
-  <si>
-    <t>Hoeveel vertrouwen heeft u in uw provinciale overheid?</t>
-  </si>
-  <si>
-    <t>Hoeveel vertrouwen heeft u in de Vlaamse overheid?</t>
-  </si>
-  <si>
-    <t>Hoeveel vertrouwen heeft u in de federale (Belgische) overheid?</t>
-  </si>
-  <si>
-    <t>Hoeveel vertrouwen heeft u in de Europese overheid?</t>
-  </si>
-  <si>
-    <t>Denkt u dat u niet voorzichtig genoeg kan zijn in de omgang met mensen of dat de meeste mensen te vertrouwen zijn?  U kan antwoorden met een score van :  0    = men kan niet voorzichtig genoeg zijn in de omgang met mensen,  10  = de meeste mensen zijn</t>
-  </si>
-  <si>
-    <t>Denkt u dat de meeste mensen zouden proberen misbruik van u te maken als zij daartoe de kans krijgen of dat zij eerlijk proberen te zijn?  U kan antwoorden met een score van :  0    = de meeste mensen zouden proberen misbruik van mij te maken als zij da</t>
-  </si>
-  <si>
-    <t>Denkt u dat de meeste mensen meestal aan zichzelf denken of dat zij meestal behulpzaam proberen te zijn?  U kan antwoorden met een score van :  0    = mensen denken meestal aan zichzelf,  10  = mensen proberen meestal behulpzaam te zijn</t>
-  </si>
-  <si>
-    <t>Indien u nog opmerkingen kwijt wil, dan kan u deze hieronder noteren.</t>
-  </si>
-  <si>
-    <t>Uniek ID per case/lijn</t>
-  </si>
-  <si>
-    <t>Ben je op deze vragenlijst terecht gekomen via een QR-code of niet?</t>
   </si>
   <si>
     <t>resp_fwdisp</t>
@@ -840,595 +687,435 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B087084C-477D-4614-B7DA-3D3808641E49}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C42" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>84</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
-      </c>
-      <c r="C49" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>100</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>102</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
-      </c>
-      <c r="C53" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
